--- a/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekouedjenevrardkarol/Documents/DONNEES EVRARD/Offre Energie PNUD actualisée/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{3994DE0F-CBBE-EE48-9EC1-1A8586B13E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFD4212C-8B8D-4B11-B894-2BA6907F61D2}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{3994DE0F-CBBE-EE48-9EC1-1A8586B13E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83286E6E-D089-420B-BB2B-F21B978A5029}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
+    <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
+    <sheet name="Projects (2)" sheetId="4" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,6 +42,24 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={11484F6E-76AC-46DF-860C-384CC606F360}</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{11484F6E-76AC-46DF-860C-384CC606F360}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This project seems to have two IDs in Quantum</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={627D9D03-17DC-483F-B04C-78289CE62CA3}</author>
   </authors>
   <commentList>
@@ -56,7 +75,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={EFB6909A-CD9A-4739-AC68-5FE8E92C6DCE}</author>
@@ -75,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="96">
   <si>
     <t>Project ID</t>
   </si>
@@ -144,6 +163,9 @@
   </si>
   <si>
     <t>number of isolated households with access to a nano-power grid</t>
+  </si>
+  <si>
+    <t>50 HH</t>
   </si>
   <si>
     <t>Note for CO: Missing targets for some outputs (all outputs need quantified targets). Please also check Project IDs and titles: the titles are the project titles, and each project should have a single ID.</t>
@@ -183,9 +205,6 @@
     <t xml:space="preserve">Résilience &amp; Dvpt Territorial </t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t>number of households connected to the power grid</t>
   </si>
   <si>
@@ -198,7 +217,7 @@
     <t>Education Services</t>
   </si>
   <si>
-    <t>number of public schools with access to energy</t>
+    <t>number of public school students with access to energy</t>
   </si>
   <si>
     <t>Medium Enterprises</t>
@@ -210,7 +229,7 @@
     <t>Health Services</t>
   </si>
   <si>
-    <t>number of hospitals benefiting from a clean energy source</t>
+    <t>number of hospital patients benefiting from a clean energy source</t>
   </si>
   <si>
     <t>5 hospitals are operational, commissionned</t>
@@ -226,40 +245,52 @@
 A household can consume around 1 to 2 kg of charcoal and/or 5 kg of wood per day. Assuming that half of the planned cooking stoves are wood-burning and the other half charcoal-burning, and assuming an energy efficiency of 50 percent, we get this result. The amount of fuel avoided is 3250 kg per day, including 750 kg of charcoal.</t>
   </si>
   <si>
+    <t>UNDP-MDG-00123355</t>
+  </si>
+  <si>
+    <t>Financement Intégré Energies R</t>
+  </si>
+  <si>
+    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar &amp; hydro power generation </t>
+  </si>
+  <si>
+    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
+  </si>
+  <si>
+    <t>Bioethanol</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
+  </si>
+  <si>
+    <t>The incubator's objective is to incubate/accelerate 15 companies/projects per incubation cycle, i.e. a total of 45 companies or start-ups.</t>
+  </si>
+  <si>
+    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>number of public schools with access to energy</t>
+  </si>
+  <si>
+    <t>number of hospitals benefiting from a clean energy source</t>
+  </si>
+  <si>
     <t>annual revenue</t>
   </si>
   <si>
-    <t>UNDP-MDG-00123355</t>
-  </si>
-  <si>
-    <t>Financement Intégré Energies R</t>
-  </si>
-  <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
-  </si>
-  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solar &amp; hydro power generation </t>
-  </si>
-  <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Bioethanol</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
-  </si>
-  <si>
-    <t>The incubator's objective is to incubate/accelerate 15 companies/projects per incubation cycle, i.e. a total of 45 companies or start-ups.</t>
-  </si>
-  <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
   </si>
   <si>
     <t xml:space="preserve">Comments </t>
@@ -360,7 +391,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -406,7 +437,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,8 +498,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -543,11 +580,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -608,33 +726,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -644,15 +735,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -664,45 +746,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -716,6 +759,156 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1027,13 +1220,21 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A7" dT="2023-07-14T07:02:41.22" personId="{2FAA20FA-7B65-4402-A66A-B9C81499D4BD}" id="{11484F6E-76AC-46DF-860C-384CC606F360}">
+    <text>This project seems to have two IDs in Quantum</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="A7" dT="2023-07-14T07:02:41.22" personId="{2FAA20FA-7B65-4402-A66A-B9C81499D4BD}" id="{627D9D03-17DC-483F-B04C-78289CE62CA3}">
     <text>This project seems to have two IDs in Quantum</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="A7" dT="2023-07-14T07:02:41.22" personId="{2FAA20FA-7B65-4402-A66A-B9C81499D4BD}" id="{EFB6909A-CD9A-4739-AC68-5FE8E92C6DCE}">
     <text>This project seems to have two IDs in Quantum</text>
@@ -1042,604 +1243,1194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B81A14-83DD-43C1-A18A-C22B7DB8731B}">
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.7109375" style="29" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="35" style="30" customWidth="1"/>
+    <col min="7" max="7" width="17" style="33" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="65.140625" style="30" customWidth="1"/>
+    <col min="10" max="12" width="9.140625" style="29"/>
+    <col min="13" max="13" width="56.85546875" style="29" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="8" customFormat="1" ht="73.5" customHeight="1">
+      <c r="A2" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="44">
+        <v>824590</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="62">
+        <v>0</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="61"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+    </row>
+    <row r="3" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A3" s="59"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="62">
+        <v>0</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="61"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+    </row>
+    <row r="4" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A4" s="57"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="62">
+        <v>0</v>
+      </c>
+      <c r="H4" s="61">
+        <v>150</v>
+      </c>
+      <c r="I4" s="61"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+    </row>
+    <row r="5" spans="1:19" s="8" customFormat="1">
+      <c r="A5" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="45">
+        <v>54790.12</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="62">
+        <v>0</v>
+      </c>
+      <c r="H5" s="61">
+        <v>0</v>
+      </c>
+      <c r="I5" s="61"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+    </row>
+    <row r="6" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A6" s="57"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="62">
+        <v>0</v>
+      </c>
+      <c r="H6" s="61">
+        <v>0</v>
+      </c>
+      <c r="I6" s="61"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+    </row>
+    <row r="7" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A7" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="45">
+        <v>2286000</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="62">
+        <v>0</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+    </row>
+    <row r="8" spans="1:19" s="8" customFormat="1" ht="32.1" customHeight="1">
+      <c r="A8" s="38"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="64">
+        <v>0</v>
+      </c>
+      <c r="H8" s="63">
+        <v>300</v>
+      </c>
+      <c r="I8" s="61"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+    </row>
+    <row r="9" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A9" s="39"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="62">
+        <v>0</v>
+      </c>
+      <c r="H9" s="61">
+        <v>63</v>
+      </c>
+      <c r="I9" s="61"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+    </row>
+    <row r="10" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A10" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="45">
+        <v>1107801</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="64">
+        <v>0</v>
+      </c>
+      <c r="H10" s="63">
+        <v>150000</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+    </row>
+    <row r="11" spans="1:19" s="8" customFormat="1" ht="153" customHeight="1">
+      <c r="A11" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="44">
+        <v>54458</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="62">
+        <v>0</v>
+      </c>
+      <c r="H11" s="61">
+        <v>3250</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+    </row>
+    <row r="12" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A12" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="48"/>
+      <c r="D12" s="45">
+        <v>8748560</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="62">
+        <v>29600</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+    </row>
+    <row r="13" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A13" s="38"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="62">
+        <v>0</v>
+      </c>
+      <c r="H13" s="62">
+        <v>8400</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+    </row>
+    <row r="14" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A14" s="38"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="62">
+        <v>0</v>
+      </c>
+      <c r="H14" s="62">
+        <v>45</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+    </row>
+    <row r="15" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A15" s="39"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="62">
+        <v>42000</v>
+      </c>
+      <c r="I15" s="61"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="G16" s="31"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="32"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="G19" s="31"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="G20" s="31"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="G22" s="31"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="G23" s="31"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="G24" s="31"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="G26" s="31"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="G27" s="31"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E6391180-236B-478C-9886-17345DBB77D7}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E31</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26D601F-6277-4308-94C5-4B46BE1AE938}">
   <dimension ref="A1:S28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" style="54" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="54" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="54" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="54" customWidth="1"/>
-    <col min="6" max="6" width="35" style="55" customWidth="1"/>
-    <col min="7" max="7" width="17" style="58" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" style="55" customWidth="1"/>
-    <col min="9" max="9" width="65.140625" style="55" customWidth="1"/>
-    <col min="10" max="12" width="9.140625" style="54"/>
-    <col min="13" max="13" width="56.85546875" style="54" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="54"/>
+    <col min="1" max="1" width="21.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.7109375" style="29" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="35" style="30" customWidth="1"/>
+    <col min="7" max="7" width="17" style="33" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="65.140625" style="30" customWidth="1"/>
+    <col min="10" max="12" width="9.140625" style="29"/>
+    <col min="13" max="13" width="56.85546875" style="29" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33" t="s">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="32" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="8" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="53">
+      <c r="C2" s="52"/>
+      <c r="D2" s="44">
         <v>824590</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="38">
-        <v>0</v>
-      </c>
-      <c r="H2" s="37">
+      <c r="G2" s="26">
+        <v>0</v>
+      </c>
+      <c r="H2" s="25">
         <v>50</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="37" t="s">
+      <c r="A3" s="59"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="38">
-        <v>0</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="F3" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
+      <c r="G3" s="26">
+        <v>0</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
     </row>
     <row r="4" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="37" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="38">
-        <v>0</v>
-      </c>
-      <c r="H4" s="37">
+      <c r="F4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0</v>
+      </c>
+      <c r="H4" s="25">
         <v>150</v>
       </c>
-      <c r="I4" s="37"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
     </row>
     <row r="5" spans="1:19" s="8" customFormat="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="53">
+      <c r="C5" s="55"/>
+      <c r="D5" s="45">
         <v>54790.12</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="37" t="s">
+      <c r="E5" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="38">
-        <v>0</v>
-      </c>
-      <c r="H5" s="37">
-        <v>0</v>
-      </c>
-      <c r="I5" s="37"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
+      <c r="F5" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="26">
+        <v>0</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
     </row>
     <row r="6" spans="1:19" s="8" customFormat="1" ht="30.75">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="37" t="s">
+      <c r="A6" s="57"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="38">
-        <v>0</v>
-      </c>
-      <c r="H6" s="37">
-        <v>0</v>
-      </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
+      <c r="F6" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
     </row>
     <row r="7" spans="1:19" s="8" customFormat="1" ht="30.75">
-      <c r="A7" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="53">
+      <c r="B7" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="45">
         <v>2286000</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="26">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+    </row>
+    <row r="8" spans="1:19" s="8" customFormat="1" ht="32.1" customHeight="1">
+      <c r="A8" s="38"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="26">
+        <v>6</v>
+      </c>
+      <c r="H8" s="25">
+        <v>8</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+    </row>
+    <row r="9" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A9" s="39"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>63</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+    </row>
+    <row r="10" spans="1:19" s="8" customFormat="1" ht="30.75">
+      <c r="A10" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="45">
+        <v>1107801</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="26">
+        <v>0</v>
+      </c>
+      <c r="H10" s="25">
+        <v>5</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+    </row>
+    <row r="11" spans="1:19" s="8" customFormat="1" ht="153" customHeight="1">
+      <c r="A11" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="38">
-        <v>0</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-    </row>
-    <row r="8" spans="1:19" s="8" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="38">
-        <v>6</v>
-      </c>
-      <c r="H8" s="37">
-        <v>8</v>
-      </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-    </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" ht="30.75">
-      <c r="A9" s="41"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="38">
-        <v>0</v>
-      </c>
-      <c r="H9" s="37">
+      <c r="C11" s="52"/>
+      <c r="D11" s="44">
+        <v>54458</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0</v>
+      </c>
+      <c r="H11" s="25">
+        <v>3250</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+    </row>
+    <row r="12" spans="1:19" s="8" customFormat="1" ht="15.95" customHeight="1">
+      <c r="A12" s="51"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-    </row>
-    <row r="10" spans="1:19" s="8" customFormat="1" ht="30.75">
-      <c r="A10" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="53">
-        <v>1107801</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="38">
-        <v>0</v>
-      </c>
-      <c r="H10" s="37">
-        <v>5</v>
-      </c>
-      <c r="I10" s="37" t="s">
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="25">
+        <v>0</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+    </row>
+    <row r="13" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A13" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="45">
+        <v>8748560</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="26">
+        <v>29600</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+    </row>
+    <row r="14" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A14" s="38"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>8400</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+    </row>
+    <row r="15" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A15" s="38"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
         <v>45</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-    </row>
-    <row r="11" spans="1:19" s="8" customFormat="1" ht="88.5" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="53">
-        <v>54458</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="38">
-        <v>0</v>
-      </c>
-      <c r="H11" s="37">
-        <v>3250</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-    </row>
-    <row r="12" spans="1:19" s="8" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="38">
-        <v>0</v>
-      </c>
-      <c r="H12" s="37">
-        <v>0</v>
-      </c>
-      <c r="I12" s="37"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-    </row>
-    <row r="13" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A13" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="53">
-        <v>8748560</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="38">
-        <v>29600</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-    </row>
-    <row r="14" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A14" s="41"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="38">
-        <v>0</v>
-      </c>
-      <c r="H14" s="38">
-        <v>8400</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-    </row>
-    <row r="15" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A15" s="41"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="37" t="s">
+      <c r="I15" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="38">
-        <v>0</v>
-      </c>
-      <c r="H15" s="38">
-        <v>45</v>
-      </c>
-      <c r="I15" s="37" t="s">
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+    </row>
+    <row r="16" spans="1:19" s="8" customFormat="1" ht="45.75">
+      <c r="A16" s="39"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-    </row>
-    <row r="16" spans="1:19" s="8" customFormat="1" ht="45.75">
-      <c r="A16" s="41"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="38">
+      <c r="G16" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="26">
         <v>42000</v>
       </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="G17" s="56"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="57"/>
-      <c r="G18" s="56"/>
+      <c r="A18" s="32"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="G19" s="56"/>
+      <c r="G19" s="31"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="G20" s="56"/>
+      <c r="G20" s="31"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="G21" s="56"/>
+      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="G22" s="56"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="G23" s="56"/>
+      <c r="G23" s="31"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="G24" s="56"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="G25" s="56"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="G26" s="56"/>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="G27" s="56"/>
+      <c r="G27" s="31"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="G28" s="56"/>
+      <c r="G28" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1660,7 +2451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -1709,19 +2500,19 @@
         <v>9</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="50" t="s">
-        <v>62</v>
+      <c r="C2" s="75"/>
+      <c r="D2" s="68" t="s">
+        <v>66</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>21</v>
@@ -1737,19 +2528,19 @@
       </c>
       <c r="I2" s="15"/>
       <c r="K2" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="45.75">
-      <c r="A3" s="45"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="51"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="69"/>
       <c r="E3" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="16">
         <v>0</v>
@@ -1760,15 +2551,15 @@
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="45.75">
-      <c r="A4" s="46"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="52"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="70"/>
       <c r="E4" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="16">
         <v>0</v>
@@ -1779,21 +2570,21 @@
       <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="50" t="s">
-        <v>63</v>
+      <c r="C5" s="75"/>
+      <c r="D5" s="68" t="s">
+        <v>67</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="16">
         <v>0</v>
@@ -1804,15 +2595,15 @@
       <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:11" ht="30.75">
-      <c r="A6" s="46"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="52"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="16">
         <v>0</v>
@@ -1823,18 +2614,18 @@
       <c r="I6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="30.75">
-      <c r="A7" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="50" t="s">
+      <c r="A7" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="50" t="s">
-        <v>64</v>
+      <c r="B7" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="68" t="s">
+        <v>68</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>36</v>
@@ -1850,15 +2641,15 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="32.1" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="51"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="14" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G8" s="16">
         <v>6</v>
@@ -1869,10 +2660,10 @@
       <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="30.75">
-      <c r="A9" s="49"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="52"/>
+      <c r="A9" s="73"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="14" t="s">
         <v>41</v>
       </c>
@@ -1896,13 +2687,13 @@
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G10" s="16">
         <v>0</v>
@@ -1915,18 +2706,18 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="50" t="s">
-        <v>66</v>
+      <c r="B11" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="75"/>
+      <c r="D11" s="68" t="s">
+        <v>70</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>47</v>
@@ -1942,15 +2733,15 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="52"/>
+      <c r="A12" s="79"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="70"/>
       <c r="E12" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -1962,41 +2753,41 @@
     </row>
     <row r="13" spans="1:11" ht="45.75">
       <c r="A13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>52</v>
-      </c>
       <c r="G13" s="16" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H13" s="16">
         <v>29600</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="45.75">
       <c r="A14" s="12"/>
       <c r="B14" s="13"/>
       <c r="C14" s="17"/>
-      <c r="D14" s="25"/>
+      <c r="D14" s="77"/>
       <c r="E14" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="16">
         <v>0</v>
@@ -2005,19 +2796,19 @@
         <v>8400</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45.75">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="25"/>
+      <c r="D15" s="77"/>
       <c r="E15" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="G15" s="16">
         <v>0</v>
@@ -2026,22 +2817,22 @@
         <v>45</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75">
       <c r="A16" s="12"/>
       <c r="B16" s="13"/>
       <c r="C16" s="17"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="76"/>
       <c r="E16" s="14" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H16" s="16">
         <v>42000</v>
@@ -2199,7 +2990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB874B5-6B34-417B-9E99-B209DC1AA263}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -2208,7 +2999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -2220,160 +3011,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="27" t="s">
-        <v>70</v>
+      <c r="A2" s="80" t="s">
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="27"/>
+      <c r="A3" s="80"/>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="27"/>
+      <c r="A4" s="80"/>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="28" t="s">
-        <v>72</v>
+      <c r="A5" s="81" t="s">
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="28"/>
+      <c r="A6" s="81"/>
       <c r="B6" t="s">
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="28"/>
+      <c r="A7" s="81"/>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="28"/>
+      <c r="A8" s="81"/>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="28"/>
+      <c r="A9" s="81"/>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="29" t="s">
-        <v>79</v>
+      <c r="A10" s="82" t="s">
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="29"/>
+      <c r="A11" s="82"/>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="30" t="s">
-        <v>82</v>
+      <c r="A12" s="83" t="s">
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="30"/>
+      <c r="A13" s="83"/>
       <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="30"/>
+      <c r="A14" s="83"/>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2388,59 +3179,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Evrard Karol EKOUEDJEN</DisplayName>
-        <AccountId>1139</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Isidore Agbokou</DisplayName>
-        <AccountId>2024</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kanil Lopes</DisplayName>
-        <AccountId>2025</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Karim Ali Ahmed</DisplayName>
-        <AccountId>1226</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chibulu Luo</DisplayName>
-        <AccountId>328</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Charles Nyandiga</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2689,7 +3427,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2698,14 +3436,67 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Evrard Karol EKOUEDJEN</DisplayName>
+        <AccountId>1139</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Isidore Agbokou</DisplayName>
+        <AccountId>2024</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kanil Lopes</DisplayName>
+        <AccountId>2025</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Karim Ali Ahmed</DisplayName>
+        <AccountId>1226</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chibulu Luo</DisplayName>
+        <AccountId>328</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Charles Nyandiga</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD93942-897D-404F-9F2B-D79DF147CC1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD93942-897D-404F-9F2B-D79DF147CC1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekouedjenevrardkarol/Documents/DONNEES EVRARD/Offre Energie PNUD actualisée/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{3994DE0F-CBBE-EE48-9EC1-1A8586B13E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE5B9FF-8865-4AE6-A3CB-1160303369AD}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{3994DE0F-CBBE-EE48-9EC1-1A8586B13E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28B827A5-B001-4A2F-8C13-BC80760E26CE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="4" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="117">
   <si>
     <t>Project ID</t>
   </si>
@@ -221,11 +221,10 @@
     <t>5 hospitals are operational, commissionned</t>
   </si>
   <si>
-    <t>UNDP-MDG-00129975
-UNDP-MDG-00129976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résilience &amp; Dvpt Territorial </t>
+    <t>Résilience &amp; Dvpt Territorial 'UNDP-MDG-00129975 &amp; UNDP-MDG-00129976</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00141254</t>
   </si>
   <si>
     <t>number of households connected to the power grid</t>
@@ -265,10 +264,10 @@
 </t>
   </si>
   <si>
-    <t>UNDP-MDG-00123355</t>
-  </si>
-  <si>
-    <t>Financement Intégré Energies R</t>
+    <t>Financement Intégré Energies R  (UNDP-MDG-00123355)</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00129782</t>
   </si>
   <si>
     <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
@@ -280,6 +279,9 @@
     <t xml:space="preserve">Solar &amp; hydro power generation </t>
   </si>
   <si>
+    <t>Mptf-Joint Sdg Fund</t>
+  </si>
+  <si>
     <t>Some Sources</t>
   </si>
   <si>
@@ -308,6 +310,13 @@
   </si>
   <si>
     <t>Agricultural Services</t>
+  </si>
+  <si>
+    <t>UNDP-MDG-00129975
+UNDP-MDG-00129976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résilience &amp; Dvpt Territorial </t>
   </si>
   <si>
     <t>Energy (MW added)</t>
@@ -327,6 +336,12 @@
   </si>
   <si>
     <t>annual revenue</t>
+  </si>
+  <si>
+    <t>UNDP-MDG-00123355</t>
+  </si>
+  <si>
+    <t>Financement Intégré Energies R</t>
   </si>
   <si>
     <t>N/A</t>
@@ -447,7 +462,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +522,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -761,8 +784,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1010,6 +1034,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1052,31 +1100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1089,7 +1113,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1442,7 +1467,7 @@
     <col min="16" max="16" width="8.85546875" style="27"/>
     <col min="17" max="17" width="16.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="30.28515625" style="27" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="22" max="16384" width="8.85546875" style="27"/>
@@ -1741,13 +1766,15 @@
       <c r="U7" s="74"/>
     </row>
     <row r="8" spans="1:23" s="6" customFormat="1" ht="45.75">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="36">
+        <v>141254</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="53"/>
       <c r="D8" s="43">
         <v>2286000</v>
       </c>
@@ -1786,10 +1813,10 @@
       <c r="U8" s="74"/>
     </row>
     <row r="9" spans="1:23" s="6" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A9" s="104"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="79"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="100"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="63" t="s">
         <v>47</v>
       </c>
@@ -1822,7 +1849,7 @@
     </row>
     <row r="10" spans="1:23" s="6" customFormat="1" ht="45.75">
       <c r="A10" s="36"/>
-      <c r="B10" s="99"/>
+      <c r="B10" s="75"/>
       <c r="C10" s="80"/>
       <c r="D10" s="77"/>
       <c r="E10" s="58" t="s">
@@ -1857,9 +1884,9 @@
     </row>
     <row r="11" spans="1:23" s="6" customFormat="1" ht="244.5">
       <c r="A11" s="49"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="101">
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="86">
         <v>54458</v>
       </c>
       <c r="E11" s="58" t="s">
@@ -1895,13 +1922,15 @@
       <c r="U11" s="74"/>
     </row>
     <row r="12" spans="1:23" s="6" customFormat="1" ht="45.75">
-      <c r="A12" s="102" t="s">
+      <c r="A12" s="87">
+        <v>129782</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="103"/>
       <c r="D12" s="64">
         <v>8748560</v>
       </c>
@@ -1920,7 +1949,9 @@
       <c r="I12" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="K12" s="25"/>
       <c r="L12" s="72" t="s">
         <v>26</v>
@@ -1934,7 +1965,7 @@
       <c r="Q12" s="65"/>
       <c r="R12" s="65"/>
       <c r="S12" s="74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T12" s="65"/>
       <c r="U12" s="74"/>
@@ -1948,7 +1979,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" s="60">
         <v>0</v>
@@ -1957,9 +1988,11 @@
         <v>8400</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="25"/>
+        <v>62</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="K13" s="25"/>
       <c r="L13" s="72" t="s">
         <v>26</v>
@@ -1982,10 +2015,10 @@
       <c r="C14" s="46"/>
       <c r="D14" s="44"/>
       <c r="E14" s="58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="60">
         <v>0</v>
@@ -1994,9 +2027,11 @@
         <v>45</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="25"/>
+        <v>65</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="K14" s="25"/>
       <c r="L14" s="72" t="s">
         <v>26</v>
@@ -2022,7 +2057,7 @@
         <v>23</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" s="60" t="s">
         <v>57</v>
@@ -2031,7 +2066,9 @@
         <v>42000</v>
       </c>
       <c r="I15" s="59"/>
-      <c r="J15" s="25"/>
+      <c r="J15" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="K15" s="25"/>
       <c r="L15" s="72" t="s">
         <v>26</v>
@@ -2045,7 +2082,7 @@
       <c r="Q15" s="65"/>
       <c r="R15" s="65"/>
       <c r="S15" s="74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T15" s="65"/>
       <c r="U15" s="74"/>
@@ -2118,8 +2155,12 @@
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C12" r:id="rId1" xr:uid="{AE69BB2D-473B-413E-9EF7-C78E869F527A}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{18E16DB8-15C1-4471-A056-CA2F3535D6FC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -2195,10 +2236,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N1" s="21" t="s">
         <v>12</v>
@@ -2262,7 +2303,7 @@
       <c r="C3" s="53"/>
       <c r="D3" s="34"/>
       <c r="E3" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>31</v>
@@ -2380,17 +2421,17 @@
     </row>
     <row r="7" spans="1:19" s="6" customFormat="1" ht="30.75">
       <c r="A7" s="36" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="43">
         <v>2286000</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>44</v>
@@ -2424,7 +2465,7 @@
         <v>47</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G8" s="24">
         <v>6</v>
@@ -2488,7 +2529,7 @@
         <v>39</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G10" s="24">
         <v>0</v>
@@ -2512,10 +2553,10 @@
     </row>
     <row r="11" spans="1:19" s="6" customFormat="1" ht="153" customHeight="1">
       <c r="A11" s="48" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="42">
@@ -2534,7 +2575,7 @@
         <v>3250</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J11" s="25"/>
       <c r="K11" s="25"/>
@@ -2556,7 +2597,7 @@
         <v>37</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G12" s="24">
         <v>0</v>
@@ -2578,23 +2619,23 @@
     </row>
     <row r="13" spans="1:19" s="6" customFormat="1" ht="45.75">
       <c r="A13" s="36" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="43">
         <v>8748560</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>56</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" s="24">
         <v>29600</v>
@@ -2622,7 +2663,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="24">
         <v>0</v>
@@ -2631,7 +2672,7 @@
         <v>8400</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J14" s="25"/>
       <c r="K14" s="25"/>
@@ -2650,10 +2691,10 @@
       <c r="C15" s="46"/>
       <c r="D15" s="44"/>
       <c r="E15" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" s="24">
         <v>0</v>
@@ -2662,7 +2703,7 @@
         <v>45</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J15" s="25"/>
       <c r="K15" s="25"/>
@@ -2684,10 +2725,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" s="24">
         <v>42000</v>
@@ -2809,19 +2850,19 @@
         <v>9</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="87" t="s">
-        <v>77</v>
+      <c r="C2" s="102"/>
+      <c r="D2" s="95" t="s">
+        <v>82</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -2841,12 +2882,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="45.75">
-      <c r="A3" s="93"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="88"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>31</v>
@@ -2860,10 +2901,10 @@
       <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:11" ht="45.75">
-      <c r="A4" s="86"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="89"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="97"/>
       <c r="E4" s="12" t="s">
         <v>33</v>
       </c>
@@ -2879,15 +2920,15 @@
       <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="87" t="s">
-        <v>78</v>
+      <c r="C5" s="102"/>
+      <c r="D5" s="95" t="s">
+        <v>83</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>35</v>
@@ -2904,10 +2945,10 @@
       <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:11" ht="30.75">
-      <c r="A6" s="86"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="89"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="97"/>
       <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
@@ -2923,18 +2964,18 @@
       <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:11" ht="30.75">
-      <c r="A7" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="87" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="87" t="s">
-        <v>79</v>
+      <c r="A7" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="102"/>
+      <c r="D7" s="95" t="s">
+        <v>84</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>44</v>
@@ -2950,15 +2991,15 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="32.1" customHeight="1">
-      <c r="A8" s="91"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="88"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="96"/>
       <c r="E8" s="12" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G8" s="14">
         <v>6</v>
@@ -2969,10 +3010,10 @@
       <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:11" ht="30.75">
-      <c r="A9" s="92"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="89"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="97"/>
       <c r="E9" s="12" t="s">
         <v>49</v>
       </c>
@@ -2996,13 +3037,13 @@
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G10" s="14">
         <v>0</v>
@@ -3015,15 +3056,15 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A11" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="87" t="s">
-        <v>81</v>
+      <c r="A11" s="105" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="102"/>
+      <c r="D11" s="95" t="s">
+        <v>86</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>35</v>
@@ -3038,19 +3079,19 @@
         <v>3250</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="89"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G12" s="14">
         <v>0</v>
@@ -3062,23 +3103,23 @@
     </row>
     <row r="13" spans="1:11" ht="45.75">
       <c r="A13" s="10" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C13" s="15"/>
-      <c r="D13" s="94" t="s">
-        <v>82</v>
+      <c r="D13" s="102" t="s">
+        <v>87</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>56</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" s="14">
         <v>29600</v>
@@ -3091,12 +3132,12 @@
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="15"/>
-      <c r="D14" s="96"/>
+      <c r="D14" s="104"/>
       <c r="E14" s="12" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="14">
         <v>0</v>
@@ -3105,19 +3146,19 @@
         <v>8400</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45.75">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="96"/>
+      <c r="D15" s="104"/>
       <c r="E15" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" s="14">
         <v>0</v>
@@ -3126,22 +3167,22 @@
         <v>45</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="15"/>
-      <c r="D16" s="95"/>
+      <c r="D16" s="103"/>
       <c r="E16" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" s="14">
         <v>42000</v>
@@ -3321,15 +3362,15 @@
         <v>23</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="108" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
@@ -3337,15 +3378,15 @@
         <v>35</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="108" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45.75">
@@ -3353,7 +3394,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
@@ -3361,15 +3402,15 @@
         <v>39</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75">
       <c r="A8" s="108" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30.75">
@@ -3377,15 +3418,15 @@
         <v>47</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="108" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B10" s="109" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3393,15 +3434,15 @@
         <v>51</v>
       </c>
       <c r="B11" s="109" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30.75">
       <c r="A12" s="108" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B12" s="67" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3409,15 +3450,15 @@
         <v>33</v>
       </c>
       <c r="B13" s="109" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="108" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B14" s="109" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3425,7 +3466,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3433,39 +3474,39 @@
         <v>37</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="108" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="108" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
       <c r="A19" s="108" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B19" s="109" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="108" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B20" s="109" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
@@ -3473,15 +3514,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="110" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="108" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B22" s="109" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3490,8 +3531,70 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Evrard Karol EKOUEDJEN</DisplayName>
+        <AccountId>1139</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Isidore Agbokou</DisplayName>
+        <AccountId>2024</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kanil Lopes</DisplayName>
+        <AccountId>2025</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Karim Ali Ahmed</DisplayName>
+        <AccountId>1226</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Chibulu Luo</DisplayName>
+        <AccountId>328</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Charles Nyandiga</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3516,6 +3619,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3595,6 +3699,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3738,76 +3847,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Evrard Karol EKOUEDJEN</DisplayName>
-        <AccountId>1139</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Isidore Agbokou</DisplayName>
-        <AccountId>2024</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kanil Lopes</DisplayName>
-        <AccountId>2025</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Karim Ali Ahmed</DisplayName>
-        <AccountId>1226</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Chibulu Luo</DisplayName>
-        <AccountId>328</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Charles Nyandiga</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD93942-897D-404F-9F2B-D79DF147CC1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F624B1C-A124-4E32-92C4-21E4FBA3A4D1}"/>
 </file>
--- a/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Madagascar - Energy Projects.xlsx
@@ -692,6 +692,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -699,9 +702,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -800,15 +800,46 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>CO validation update</author>
     <author>tc={11484F6E-76AC-46DF-860C-384CC606F360}</author>
   </authors>
   <commentList>
-    <comment ref="A9" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="1" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     This project seems to have two IDs in Quantum</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
       </text>
     </comment>
   </commentList>
@@ -1592,15 +1623,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="112" t="n"/>
-      <c r="M8" s="112" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K8" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="113" t="n"/>
+      <c r="M8" s="59" t="n"/>
       <c r="N8" s="25" t="n"/>
       <c r="O8" s="25" t="n"/>
       <c r="P8" s="65" t="n"/>
@@ -1630,9 +1657,9 @@
       <c r="D9" s="43" t="n">
         <v>2286000</v>
       </c>
-      <c r="E9" s="113" t="n"/>
-      <c r="F9" s="113" t="n"/>
-      <c r="G9" s="113" t="n"/>
+      <c r="E9" s="114" t="n"/>
+      <c r="F9" s="114" t="n"/>
+      <c r="G9" s="114" t="n"/>
       <c r="H9" s="43" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -1837,15 +1864,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K13" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="112" t="n"/>
-      <c r="M13" s="112" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K13" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="113" t="n"/>
+      <c r="M13" s="59" t="n"/>
       <c r="N13" s="25" t="n"/>
       <c r="O13" s="25" t="n"/>
       <c r="P13" s="65" t="n"/>
@@ -1875,9 +1898,9 @@
       <c r="D14" s="64" t="n">
         <v>8748560</v>
       </c>
-      <c r="E14" s="114" t="n"/>
-      <c r="F14" s="114" t="n"/>
-      <c r="G14" s="114" t="n"/>
+      <c r="E14" s="115" t="n"/>
+      <c r="F14" s="115" t="n"/>
+      <c r="G14" s="115" t="n"/>
       <c r="H14" s="64" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2101,15 +2124,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K18" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="115" t="n"/>
-      <c r="M18" s="112" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="K18" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="112" t="n"/>
+      <c r="M18" s="59" t="n"/>
       <c r="N18" s="25" t="n"/>
       <c r="O18" s="25" t="n"/>
       <c r="P18" s="65" t="n"/>
@@ -2160,7 +2179,7 @@
       <c r="K30" s="29" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2187,12 +2206,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
